--- a/web/public/forms/orig/o-deck-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-deck-gyehoekseo.xlsx
@@ -889,7 +889,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1015,7 +1015,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="P1" s="68" t="inlineStr">
@@ -1996,7 +1996,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="68" t="inlineStr">
@@ -3340,7 +3340,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="68" t="inlineStr">
@@ -4408,7 +4408,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="P1" s="2" t="inlineStr">
@@ -6537,7 +6537,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8921,7 +8921,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="68" t="inlineStr">
@@ -9009,7 +9009,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="68" t="inlineStr">
@@ -9487,7 +9487,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="68" t="inlineStr">

--- a/web/public/forms/orig/o-deck-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-deck-gyehoekseo.xlsx
@@ -861,7 +861,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="P1" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
